--- a/medford_lor_mikroskopy.xlsx
+++ b/medford_lor_mikroskopy.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ЛОР микроскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS — всего 6 позиций.</t>
+          <t>ЛОР микроскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_lor_mikroskopy.xlsx
+++ b/medford_lor_mikroskopy.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать лОР микроскопы для клиники?</t>
+          <t>Чем диагностический ЛОР-микроскоп отличается от операционного?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Страна производства, Производитель, Объектив, мм, Радиус освещаемого поля, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Диагностический микроскоп компактен и предназначен для углублённого осмотра труднодоступных участков. Операционный даёт максимально увеличивающую оптику, широкое поле зрения и настраиваемое фокусное расстояние для сложных вмешательств — тимпанопластики, стапедопластики, септопластики. Операционные модели дороже за счёт оптики и вариозума.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Какое рабочее расстояние объектива выбрать?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Оптимальным считается 200–250 мм: между линзой и пациентом остаётся место для работы инструментами. Слишком короткое расстояние стесняет манипуляции. У модели каталога Chammed OMS-2300 фокусное расстояние 170 мм и объектив 200 мм. Параметр под методику уточняют при подборе.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Что лучше: ступенчатое увеличение или вариозум?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены ATMOS. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Ступенчатый переключатель (несколько фиксированных ступеней) достаточен для амбулаторного осмотра и дешевле. Плавное изменение — вариозум — нужно в хирургии, где кратность меняют по ходу операции, но он значительно удорожает прибор. Выбор зависит от того, оперирует ли врач под микроскопом.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Можно ли использовать в ЛОР офтальмологический или зуботехнический микроскоп?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Нет. Использование в ЛОР-практике микроскопов, предназначенных для других целей, не допускается законом и делает невозможным лицензирование кабинета. Прибор должен иметь действующее регистрационное удостоверение Росздравнадзора именно для оториноларингологического применения. Область применения указана в РУ, и её сверяют до покупки.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>LED или галоген в подсветке микроскопа?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>LED-освещение предпочтительнее галогенового: стабильная цветовая температура, долгий срок службы и отсутствие сильного нагрева. Это важно для корректной оценки тканей и комфорта при длительной работе. Галоген дешевле в замене ламп, но уступает по стабильности и нагреву.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит микроскоп для лечения зубов?</t>
+          <t>Можно ли подключить к микроскопу видеокамеру?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Многие ЛОР-микроскопы поддерживают подключение видеокамеры через порт или делитель для документирования и трансляции процедур. Возможность и тип крепления зависят от модели — уточните конфигурацию оптической головки. Тринокулярная схема с отдельным портом упрощает установку камеры.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Какой микроскоп входит в топ-10 лучших?</t>
+          <t>Предоставляете ли гарантию и сервис на микроскопы?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>На поставляемые ЛОР-микроскопы распространяется гарантия, а обслуживание и ремонт оптики и механики выполняет собственный инженерный сервис. Условия по конкретной модели, срок гарантии и порядок обращения уточняйте у менеджера при оформлении. Для операционных моделей отдельно оговаривают проверку оптической головки и системы противовесов.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ЛОР микроскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS.</t>
+          <t>ЛОР-микроскопы — это оптические приборы для детального осмотра и микрохирургии структур уха, горла и носа. В каталоге представлены оториноларингологические микроскопы Chammed (OMS-2350, OMS-2300, ТМ03-34), смотровые модели ATMOS i View 21 и 31 и операционный ЛОР-микроскоп Mega Medical MICRO-100. У Chammed OMS-2300 рабочее расстояние 170 мм, объектив 200 мм, ступенчатое увеличение 0,4–2,5х и угол поля зрения 45°. Приборы применяют в диагностике и в микрохирургических вмешательствах.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Виды ЛОР-микроскопов по назначению</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое лОР микроскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3364,235 +3364,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Виды ЛОР-микроскопов по назначению</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Тип</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Задача</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Страна производства</t>
+          <t>Оптика и увеличение</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Производитель</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Объектив, мм</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Радиус освещаемого поля, мм</t>
+          <t>Пример</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Микроскоп оториноларингологический Chammed OMS-2350</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>Диагностический</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Углублённый осмотр труднодоступных зон</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Южная Корея</t>
+          <t>Ступенчатое увеличение</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>67308</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>ATMOS i View 21/31, Chammed OMS-2300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Микроскоп смотровой ATMOS i View 31</t>
+          <t>Операционный</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ATMOS</t>
+          <t>Сложные микрохирургические вмешательства</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Германия</t>
+          <t>Широкое поле, настраиваемый фокус</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>67319</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mega Medical MICRO-100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Микроскоп смотровой ATMOS i View 21</t>
+          <t>Мультифункциональный</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>ATMOS</t>
+          <t>ЛОР и смежная микрохирургия</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Германия</t>
+          <t>Универсальная оптика</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>67319</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Микроскоп оториноларингологический Chammed ТМ03-34</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Южная Корея</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>67308</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Микроскоп оториноларингологический Chammed OMS-2300</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Операционный ЛОР-микроскоп Mega Medical MICRO-100</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Chammed OMS-2350, ТМ03-34</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3604,7 +3482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3930,12 +3808,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите задачу: осмотр или операции</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается лОР микроскопы: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Диагностические микроскопы компактны и подходят для углублённого осмотра труднодоступных участков (смотровые ATMOS i View 21/31). Операционные модели дают максимальную оптику, широкое поле и настраиваемый фокус для сложных вмешательств (Mega Medical MICRO-100). От задачи зависит класс прибора и цена.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3975,12 +3853,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите тип увеличения</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Для амбулаторного приёма обычно достаточно ступенчатого переключателя на несколько ступеней — например, у Chammed OMS-2300 это 0,4–2,5х. Для хирургии нужен плавный вариозум, который удобнее в работе, но значительно удорожает прибор. Выбор зависит от того, оперирует ли врач под микроскопом.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -4020,12 +3898,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Проверьте рабочее расстояние объектива</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Страна производства, Производитель, Объектив, мм, Радиус освещаемого поля, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Оптимальное рабочее расстояние — 200–250 мм: между линзой и пациентом остаётся достаточно места для манипуляций инструментами. У Chammed OMS-2300 фокусное расстояние 170 мм, объектив 200 мм. Уточните этот параметр под методику, чтобы врачу было удобно работать инструментом.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -4065,12 +3943,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените источник света</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: ATMOS.</t>
+          <t>LED-подсветка предпочтительнее галогеновой: она стабильнее по цветовой температуре, дольше служит и меньше нагревается. Стабильный холодный свет важен для корректной оценки тканей при длительной работе. Уточните тип освещения и наличие регулировки яркости у конкретной модели.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4110,12 +3988,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Подберите размещение и эргономику</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>По способу размещения микроскопы бывают настольными, настенными, потолочными и напольными — выбор зависит от кабинета. Для длительной работы важны регулируемые наглазники, настройка межзрачкового расстояния и система противовесов, снижающая нагрузку на врача. Оцените эргономику под рост и посадку специалиста.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -4155,12 +4033,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните РУ и опции документирования</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Убедитесь, что модель имеет действующее РУ Росздравнадзора именно для ЛОР-применения — приборы для офтальмологии или стоматологии не подходят и мешают лицензированию. Уточните возможность подключения видеокамеры, наличие светофильтров (жёлтые, зелёные) для контраста и комплект насадок.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -4210,7 +4088,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>ЛОР микроскопы подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены ATMOS. При выборе обращают внимание на страна производства, производитель, объектив, радиус освещаемого поля, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>В ЛОР-микроскопе для меня ключевое — рабочее расстояние объектива и тип увеличения. Для амбулаторного приёма достаточно ступенчатого переключателя, а для хирургии нужен плавный вариозум, который заметно дороже. Рабочее расстояние 200–250 мм оставляет место для инструментов между линзой и пациентом. LED-подсветку предпочитаю за стабильную цветовую температуру. Обязательно проверяю, что у модели есть РУ именно на ЛОР-применение, а не на смежную специальность.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4494,13 +4372,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое лОР микроскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>ЛОР микроскопы — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов ATMOS. Подберём вариант под задачи вашего отделения.</t>
+          <t>ЛОР-микроскоп — оптический прибор для детального осмотра и микрохирургии уха, горла и носа. Основные узлы: оптическая система (часто стереоскопическая), освещение (LED предпочтительнее галогена), опорная конструкция и бинокулярная насадка. По назначению выделяют диагностические, операционные и мультифункциональные модели, по размещению — настольные, настенные, потолочные и напольные. При выборе смотрят на рабочее расстояние объектива (оптимально 200–250 мм), тип увеличения (ступени или вариозум) и эргономику. Прибор обязан иметь РУ Росздравнадзора именно для оториноларингологического применения.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4537,13 +4415,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое ЛОР-микроскоп</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Страна производства, Производитель, Объектив, мм, Радиус освещаемого поля, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>ЛОР-микроскоп (оториноларингологический микроскоп) — специализированный оптический прибор для детального осмотра структур уха, горла и носа. Он повышает точность диагностики и делает возможными малоинвазивные вмешательства. Прибор применяют для осмотра слизистых, выявления полипов и новообразований, а также при тимпанопластике, стапедопластике и септопластике.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4580,13 +4458,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Как устроен ЛОР-микроскоп</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Основные узлы прибора: оптическая система из линз с многократным увеличением, часто стереоскопическая; система освещения, чаще светодиодная (LED) с холодным стабильным светом; устойчивая опорная конструкция для точного позиционирования головки; бинокулярная насадка для осмотра двумя глазами, снижающая нагрузку при длительной работе.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4623,13 +4501,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Виды и размещение</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>По назначению различают диагностические микроскопы для углублённого осмотра, операционные с максимальной оптикой и настраиваемым фокусом, а также мультифункциональные модели. По способу размещения — настольные, настенные, потолочные и напольные. В каталоге есть смотровые ATMOS i View и операционный Mega Medical MICRO-100.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4646,6 +4524,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Характеристики при выборе</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Ключевые параметры: тип увеличения (ступенчатый для приёма, вариозум для хирургии), рабочее расстояние объектива (оптимально 200–250 мм), тип освещения (LED предпочтительнее), эргономика (наглазники, межзрачковое расстояние, противовесы) и опции — светофильтры и подключение видеокамеры. У Chammed OMS-2300 указаны объектив 200 мм и увеличение 0,4–2,5х.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>lor_mikroskopy</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
